--- a/outputs/Block6C_Margin_Summary.xlsx
+++ b/outputs/Block6C_Margin_Summary.xlsx
@@ -19,7 +19,7 @@
     <t>Chamber</t>
   </si>
   <si>
-    <t>Central Democratic Margin</t>
+    <t>Official Central Democratic Margin</t>
   </si>
   <si>
     <t>Mean Simulated Margin</t>
@@ -435,25 +435,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C2">
-        <v>14.05</v>
+        <v>31.91</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>-21</v>
+        <v>-3</v>
       </c>
       <c r="F2">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="G2">
-        <v>74.58</v>
+        <v>92.2</v>
       </c>
       <c r="H2">
-        <v>25.42</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -461,25 +461,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>-2.12</v>
+        <v>0.15</v>
       </c>
       <c r="D3">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>22.54</v>
+        <v>43.04</v>
       </c>
       <c r="H3">
-        <v>77.45999999999999</v>
+        <v>56.96</v>
       </c>
     </row>
   </sheetData>
